--- a/inStockInventory_20260915.xlsx
+++ b/inStockInventory_20260915.xlsx
@@ -153,9 +153,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>0</col>
+      <col>9</col>
       <colOff>0</colOff>
-      <row>26</row>
+      <row>1</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="3095625" cy="4371975"/>
@@ -180,7 +180,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>51</row>
+      <row>13</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="3095625" cy="4381500"/>
@@ -191,6 +191,56 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>13</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3095625" cy="4371975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>25</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3095625" cy="4371975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -493,7 +543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H56"/>
+  <dimension ref="A1:Q31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -504,6 +554,14 @@
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -532,6 +590,31 @@
           <t>Price</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Product Picture</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Product Name</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Colors</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Qty</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>Price</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="E2" t="inlineStr">
@@ -547,6 +630,25 @@
       <c r="G2" t="n">
         <v>107</v>
       </c>
+      <c r="H2" t="n">
+        <v>23</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>AS60158 SET</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>BG</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>117</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>23.5</v>
+      </c>
     </row>
     <row r="3">
       <c r="E3" t="inlineStr">
@@ -562,6 +664,25 @@
       <c r="G3" t="n">
         <v>249</v>
       </c>
+      <c r="H3" t="n">
+        <v>23</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>AS60158 SET</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>BK</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>357</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>23.5</v>
+      </c>
     </row>
     <row r="4">
       <c r="E4" t="inlineStr">
@@ -577,6 +698,25 @@
       <c r="G4" t="n">
         <v>155</v>
       </c>
+      <c r="H4" t="n">
+        <v>23</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>AS60158 SET</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>174</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>23.5</v>
+      </c>
     </row>
     <row r="5">
       <c r="E5" t="inlineStr">
@@ -592,41 +732,272 @@
       <c r="G5" t="n">
         <v>101</v>
       </c>
+      <c r="H5" t="n">
+        <v>23</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>AS60158 SET</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>KHA</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>113</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>CR20202</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>BK</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>163</v>
+      </c>
+      <c r="H14" t="n">
+        <v>23</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>HL60121 SET</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>BGY</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>CR20202</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>GY</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>89</v>
+      </c>
+      <c r="H15" t="n">
+        <v>23</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>HL60121 SET</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>BK</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>250</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>CR20202</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>RBL</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>98</v>
+      </c>
+      <c r="H16" t="n">
+        <v>23</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>HL60121 SET</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>74</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>CR20202</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>RUST</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>62</v>
+      </c>
+      <c r="H17" t="n">
+        <v>23</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>HL60121 SET</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>CF</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>105</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>CR20202</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>TP</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>12</v>
+      </c>
+      <c r="H18" t="n">
+        <v>23</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>HL60121 SET</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>KHA</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>42</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>HL60121 SET</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>HL60143 SET</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>BG</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>123</v>
+      </c>
+      <c r="H26" t="n">
+        <v>23.25</v>
+      </c>
     </row>
     <row r="27">
       <c r="E27" t="inlineStr">
         <is>
-          <t>AS60158 SET</t>
+          <t>HL60143 SET</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>BG</t>
+          <t>BK</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>117</v>
+        <v>434</v>
+      </c>
+      <c r="H27" t="n">
+        <v>23.25</v>
       </c>
     </row>
     <row r="28">
       <c r="E28" t="inlineStr">
         <is>
-          <t>AS60158 SET</t>
+          <t>HL60143 SET</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>BK</t>
+          <t>BL</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>357</v>
+        <v>19</v>
+      </c>
+      <c r="H28" t="n">
+        <v>23.25</v>
       </c>
     </row>
     <row r="29">
       <c r="E29" t="inlineStr">
         <is>
-          <t>AS60158 SET</t>
+          <t>HL60143 SET</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -635,13 +1006,16 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>174</v>
+        <v>202</v>
+      </c>
+      <c r="H29" t="n">
+        <v>23.25</v>
       </c>
     </row>
     <row r="30">
       <c r="E30" t="inlineStr">
         <is>
-          <t>AS60158 SET</t>
+          <t>HL60143 SET</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -650,82 +1024,28 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>CR20202</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>BK</t>
-        </is>
-      </c>
-      <c r="G52" t="n">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>CR20202</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>GY</t>
-        </is>
-      </c>
-      <c r="G53" t="n">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>CR20202</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>RBL</t>
-        </is>
-      </c>
-      <c r="G54" t="n">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>CR20202</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>RUST</t>
-        </is>
-      </c>
-      <c r="G55" t="n">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>CR20202</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
+        <v>101</v>
+      </c>
+      <c r="H30" t="n">
+        <v>23.25</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>HL60143 SET</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
         <is>
           <t>TP</t>
         </is>
       </c>
-      <c r="G56" t="n">
-        <v>12</v>
+      <c r="G31" t="n">
+        <v>91</v>
+      </c>
+      <c r="H31" t="n">
+        <v>23.25</v>
       </c>
     </row>
   </sheetData>

--- a/inStockInventory_20260915.xlsx
+++ b/inStockInventory_20260915.xlsx
@@ -133,7 +133,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="3095625" cy="4371975"/>
+    <ext cx="2743200" cy="3876675"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -158,7 +158,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="3095625" cy="4371975"/>
+    <ext cx="2743200" cy="3876675"/>
     <pic>
       <nvPicPr>
         <cNvPr id="2" name="Image 2" descr="Picture"/>
@@ -180,10 +180,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>13</row>
+      <row>12</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="3095625" cy="4381500"/>
+    <ext cx="2743200" cy="3876675"/>
     <pic>
       <nvPicPr>
         <cNvPr id="3" name="Image 3" descr="Picture"/>
@@ -205,10 +205,10 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>13</row>
+      <row>12</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="3095625" cy="4371975"/>
+    <ext cx="2743200" cy="3876675"/>
     <pic>
       <nvPicPr>
         <cNvPr id="4" name="Image 4" descr="Picture"/>
@@ -230,10 +230,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>25</row>
+      <row>23</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="3095625" cy="4371975"/>
+    <ext cx="2743200" cy="3867150"/>
     <pic>
       <nvPicPr>
         <cNvPr id="5" name="Image 5" descr="Picture"/>
@@ -543,7 +543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q31"/>
+  <dimension ref="A1:Q29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -616,7 +616,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="35" customHeight="1">
       <c r="E2" t="inlineStr">
         <is>
           <t>AS30188</t>
@@ -650,7 +650,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="35" customHeight="1">
       <c r="E3" t="inlineStr">
         <is>
           <t>AS30188</t>
@@ -684,7 +684,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="35" customHeight="1">
       <c r="E4" t="inlineStr">
         <is>
           <t>AS30188</t>
@@ -718,7 +718,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="35" customHeight="1">
       <c r="E5" t="inlineStr">
         <is>
           <t>AS30188</t>
@@ -752,7 +752,46 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="14">
+    <row r="6" ht="35" customHeight="1"/>
+    <row r="7" ht="35" customHeight="1"/>
+    <row r="8" ht="35" customHeight="1"/>
+    <row r="9" ht="35" customHeight="1"/>
+    <row r="10" ht="35" customHeight="1"/>
+    <row r="13" ht="35" customHeight="1">
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>CR20202</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>BK</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>163</v>
+      </c>
+      <c r="H13" t="n">
+        <v>23</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>HL60121 SET</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>BGY</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="14" ht="35" customHeight="1">
       <c r="E14" t="inlineStr">
         <is>
           <t>CR20202</t>
@@ -760,11 +799,11 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>BK</t>
+          <t>GY</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>163</v>
+        <v>89</v>
       </c>
       <c r="H14" t="n">
         <v>23</v>
@@ -776,17 +815,17 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>BGY</t>
+          <t>BK</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>7</v>
+        <v>250</v>
       </c>
       <c r="Q14" t="n">
         <v>23.5</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="35" customHeight="1">
       <c r="E15" t="inlineStr">
         <is>
           <t>CR20202</t>
@@ -794,11 +833,11 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>GY</t>
+          <t>RBL</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="H15" t="n">
         <v>23</v>
@@ -810,17 +849,17 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>BK</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>250</v>
+        <v>74</v>
       </c>
       <c r="Q15" t="n">
         <v>23.5</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="35" customHeight="1">
       <c r="E16" t="inlineStr">
         <is>
           <t>CR20202</t>
@@ -828,11 +867,11 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>RBL</t>
+          <t>RUST</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>98</v>
+        <v>62</v>
       </c>
       <c r="H16" t="n">
         <v>23</v>
@@ -844,17 +883,17 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>74</v>
+        <v>105</v>
       </c>
       <c r="Q16" t="n">
         <v>23.5</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="35" customHeight="1">
       <c r="E17" t="inlineStr">
         <is>
           <t>CR20202</t>
@@ -862,11 +901,11 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>RUST</t>
+          <t>TP</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>62</v>
+        <v>12</v>
       </c>
       <c r="H17" t="n">
         <v>23</v>
@@ -878,33 +917,17 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>105</v>
+        <v>42</v>
       </c>
       <c r="Q17" t="n">
         <v>23.5</v>
       </c>
     </row>
-    <row r="18">
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>CR20202</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>TP</t>
-        </is>
-      </c>
-      <c r="G18" t="n">
-        <v>12</v>
-      </c>
-      <c r="H18" t="n">
-        <v>23</v>
-      </c>
+    <row r="18" ht="35" customHeight="1">
       <c r="N18" t="inlineStr">
         <is>
           <t>HL60121 SET</t>
@@ -912,35 +935,56 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>ST</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="Q18" t="n">
         <v>23.5</v>
       </c>
     </row>
-    <row r="19">
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>HL60121 SET</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>ST</t>
-        </is>
-      </c>
-      <c r="P19" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>23.5</v>
-      </c>
-    </row>
-    <row r="26">
+    <row r="19" ht="35" customHeight="1"/>
+    <row r="20" ht="35" customHeight="1"/>
+    <row r="21" ht="35" customHeight="1"/>
+    <row r="24" ht="35" customHeight="1">
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>HL60143 SET</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>BG</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>123</v>
+      </c>
+      <c r="H24" t="n">
+        <v>23.25</v>
+      </c>
+    </row>
+    <row r="25" ht="35" customHeight="1">
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>HL60143 SET</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>BK</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>434</v>
+      </c>
+      <c r="H25" t="n">
+        <v>23.25</v>
+      </c>
+    </row>
+    <row r="26" ht="35" customHeight="1">
       <c r="E26" t="inlineStr">
         <is>
           <t>HL60143 SET</t>
@@ -948,17 +992,17 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>BG</t>
+          <t>BL</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>123</v>
+        <v>19</v>
       </c>
       <c r="H26" t="n">
         <v>23.25</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" ht="35" customHeight="1">
       <c r="E27" t="inlineStr">
         <is>
           <t>HL60143 SET</t>
@@ -966,17 +1010,17 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>BK</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>434</v>
+        <v>202</v>
       </c>
       <c r="H27" t="n">
         <v>23.25</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" ht="35" customHeight="1">
       <c r="E28" t="inlineStr">
         <is>
           <t>HL60143 SET</t>
@@ -984,17 +1028,17 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>BL</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>19</v>
+        <v>101</v>
       </c>
       <c r="H28" t="n">
         <v>23.25</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" ht="35" customHeight="1">
       <c r="E29" t="inlineStr">
         <is>
           <t>HL60143 SET</t>
@@ -1002,52 +1046,19 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>TP</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>202</v>
+        <v>91</v>
       </c>
       <c r="H29" t="n">
         <v>23.25</v>
       </c>
     </row>
-    <row r="30">
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>HL60143 SET</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>KHA</t>
-        </is>
-      </c>
-      <c r="G30" t="n">
-        <v>101</v>
-      </c>
-      <c r="H30" t="n">
-        <v>23.25</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>HL60143 SET</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>TP</t>
-        </is>
-      </c>
-      <c r="G31" t="n">
-        <v>91</v>
-      </c>
-      <c r="H31" t="n">
-        <v>23.25</v>
-      </c>
-    </row>
+    <row r="30" ht="35" customHeight="1"/>
+    <row r="31" ht="35" customHeight="1"/>
+    <row r="32" ht="35" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/inStockInventory_20260915.xlsx
+++ b/inStockInventory_20260915.xlsx
@@ -180,7 +180,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>12</row>
+      <row>14</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2743200" cy="3876675"/>
@@ -205,7 +205,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>12</row>
+      <row>14</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2743200" cy="3876675"/>
@@ -230,7 +230,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>23</row>
+      <row>40</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2743200" cy="3867150"/>
@@ -543,7 +543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q29"/>
+  <dimension ref="A1:Q46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -616,7 +616,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="35" customHeight="1">
+    <row r="2">
       <c r="E2" t="inlineStr">
         <is>
           <t>AS30188</t>
@@ -650,7 +650,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="3" ht="35" customHeight="1">
+    <row r="3">
       <c r="E3" t="inlineStr">
         <is>
           <t>AS30188</t>
@@ -684,7 +684,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="4" ht="35" customHeight="1">
+    <row r="4">
       <c r="E4" t="inlineStr">
         <is>
           <t>AS30188</t>
@@ -718,7 +718,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="5" ht="35" customHeight="1">
+    <row r="5">
       <c r="E5" t="inlineStr">
         <is>
           <t>AS30188</t>
@@ -752,92 +752,19 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="6" ht="35" customHeight="1"/>
-    <row r="7" ht="35" customHeight="1"/>
-    <row r="8" ht="35" customHeight="1"/>
-    <row r="9" ht="35" customHeight="1"/>
-    <row r="10" ht="35" customHeight="1"/>
-    <row r="13" ht="35" customHeight="1">
-      <c r="E13" t="inlineStr">
+    <row r="15">
+      <c r="E15" t="inlineStr">
         <is>
           <t>CR20202</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>BK</t>
         </is>
       </c>
-      <c r="G13" t="n">
+      <c r="G15" t="n">
         <v>163</v>
-      </c>
-      <c r="H13" t="n">
-        <v>23</v>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>HL60121 SET</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>BGY</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>23.5</v>
-      </c>
-    </row>
-    <row r="14" ht="35" customHeight="1">
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>CR20202</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>GY</t>
-        </is>
-      </c>
-      <c r="G14" t="n">
-        <v>89</v>
-      </c>
-      <c r="H14" t="n">
-        <v>23</v>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>HL60121 SET</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>BK</t>
-        </is>
-      </c>
-      <c r="P14" t="n">
-        <v>250</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>23.5</v>
-      </c>
-    </row>
-    <row r="15" ht="35" customHeight="1">
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>CR20202</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>RBL</t>
-        </is>
-      </c>
-      <c r="G15" t="n">
-        <v>98</v>
       </c>
       <c r="H15" t="n">
         <v>23</v>
@@ -849,17 +776,17 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>BGY</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>74</v>
+        <v>7</v>
       </c>
       <c r="Q15" t="n">
         <v>23.5</v>
       </c>
     </row>
-    <row r="16" ht="35" customHeight="1">
+    <row r="16">
       <c r="E16" t="inlineStr">
         <is>
           <t>CR20202</t>
@@ -867,11 +794,11 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>RUST</t>
+          <t>GY</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>62</v>
+        <v>89</v>
       </c>
       <c r="H16" t="n">
         <v>23</v>
@@ -883,17 +810,17 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>BK</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>105</v>
+        <v>250</v>
       </c>
       <c r="Q16" t="n">
         <v>23.5</v>
       </c>
     </row>
-    <row r="17" ht="35" customHeight="1">
+    <row r="17">
       <c r="E17" t="inlineStr">
         <is>
           <t>CR20202</t>
@@ -901,11 +828,11 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>RBL</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>12</v>
+        <v>98</v>
       </c>
       <c r="H17" t="n">
         <v>23</v>
@@ -917,17 +844,33 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="Q17" t="n">
         <v>23.5</v>
       </c>
     </row>
-    <row r="18" ht="35" customHeight="1">
+    <row r="18">
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>CR20202</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>RUST</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>62</v>
+      </c>
+      <c r="H18" t="n">
+        <v>23</v>
+      </c>
       <c r="N18" t="inlineStr">
         <is>
           <t>HL60121 SET</t>
@@ -935,130 +878,176 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1</v>
+        <v>105</v>
       </c>
       <c r="Q18" t="n">
         <v>23.5</v>
       </c>
     </row>
-    <row r="19" ht="35" customHeight="1"/>
-    <row r="20" ht="35" customHeight="1"/>
-    <row r="21" ht="35" customHeight="1"/>
-    <row r="24" ht="35" customHeight="1">
-      <c r="E24" t="inlineStr">
+    <row r="19">
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>CR20202</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>TP</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>12</v>
+      </c>
+      <c r="H19" t="n">
+        <v>23</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>HL60121 SET</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>KHA</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>42</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>HL60121 SET</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="E41" t="inlineStr">
         <is>
           <t>HL60143 SET</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>BG</t>
         </is>
       </c>
-      <c r="G24" t="n">
+      <c r="G41" t="n">
         <v>123</v>
       </c>
-      <c r="H24" t="n">
+      <c r="H41" t="n">
         <v>23.25</v>
       </c>
     </row>
-    <row r="25" ht="35" customHeight="1">
-      <c r="E25" t="inlineStr">
+    <row r="42">
+      <c r="E42" t="inlineStr">
         <is>
           <t>HL60143 SET</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>BK</t>
         </is>
       </c>
-      <c r="G25" t="n">
+      <c r="G42" t="n">
         <v>434</v>
       </c>
-      <c r="H25" t="n">
+      <c r="H42" t="n">
         <v>23.25</v>
       </c>
     </row>
-    <row r="26" ht="35" customHeight="1">
-      <c r="E26" t="inlineStr">
+    <row r="43">
+      <c r="E43" t="inlineStr">
         <is>
           <t>HL60143 SET</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>BL</t>
         </is>
       </c>
-      <c r="G26" t="n">
+      <c r="G43" t="n">
         <v>19</v>
       </c>
-      <c r="H26" t="n">
+      <c r="H43" t="n">
         <v>23.25</v>
       </c>
     </row>
-    <row r="27" ht="35" customHeight="1">
-      <c r="E27" t="inlineStr">
+    <row r="44">
+      <c r="E44" t="inlineStr">
         <is>
           <t>HL60143 SET</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>BR</t>
         </is>
       </c>
-      <c r="G27" t="n">
+      <c r="G44" t="n">
         <v>202</v>
       </c>
-      <c r="H27" t="n">
+      <c r="H44" t="n">
         <v>23.25</v>
       </c>
     </row>
-    <row r="28" ht="35" customHeight="1">
-      <c r="E28" t="inlineStr">
+    <row r="45">
+      <c r="E45" t="inlineStr">
         <is>
           <t>HL60143 SET</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>KHA</t>
         </is>
       </c>
-      <c r="G28" t="n">
+      <c r="G45" t="n">
         <v>101</v>
       </c>
-      <c r="H28" t="n">
+      <c r="H45" t="n">
         <v>23.25</v>
       </c>
     </row>
-    <row r="29" ht="35" customHeight="1">
-      <c r="E29" t="inlineStr">
+    <row r="46">
+      <c r="E46" t="inlineStr">
         <is>
           <t>HL60143 SET</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>TP</t>
         </is>
       </c>
-      <c r="G29" t="n">
+      <c r="G46" t="n">
         <v>91</v>
       </c>
-      <c r="H29" t="n">
+      <c r="H46" t="n">
         <v>23.25</v>
       </c>
     </row>
-    <row r="30" ht="35" customHeight="1"/>
-    <row r="31" ht="35" customHeight="1"/>
-    <row r="32" ht="35" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/inStockInventory_20260915.xlsx
+++ b/inStockInventory_20260915.xlsx
@@ -180,7 +180,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>14</row>
+      <row>26</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2743200" cy="3876675"/>
@@ -205,7 +205,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>14</row>
+      <row>26</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2743200" cy="3876675"/>
@@ -230,7 +230,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>40</row>
+      <row>76</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2743200" cy="3867150"/>
@@ -543,7 +543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q46"/>
+  <dimension ref="A1:Q82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -752,299 +752,299 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="15">
-      <c r="E15" t="inlineStr">
+    <row r="27">
+      <c r="E27" t="inlineStr">
         <is>
           <t>CR20202</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>BK</t>
         </is>
       </c>
-      <c r="G15" t="n">
+      <c r="G27" t="n">
         <v>163</v>
       </c>
-      <c r="H15" t="n">
+      <c r="H27" t="n">
         <v>23</v>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>HL60121 SET</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>BGY</t>
         </is>
       </c>
-      <c r="P15" t="n">
+      <c r="P27" t="n">
         <v>7</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="Q27" t="n">
         <v>23.5</v>
       </c>
     </row>
-    <row r="16">
-      <c r="E16" t="inlineStr">
+    <row r="28">
+      <c r="E28" t="inlineStr">
         <is>
           <t>CR20202</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>GY</t>
         </is>
       </c>
-      <c r="G16" t="n">
+      <c r="G28" t="n">
         <v>89</v>
       </c>
-      <c r="H16" t="n">
+      <c r="H28" t="n">
         <v>23</v>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>HL60121 SET</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t>BK</t>
         </is>
       </c>
-      <c r="P16" t="n">
+      <c r="P28" t="n">
         <v>250</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="Q28" t="n">
         <v>23.5</v>
       </c>
     </row>
-    <row r="17">
-      <c r="E17" t="inlineStr">
+    <row r="29">
+      <c r="E29" t="inlineStr">
         <is>
           <t>CR20202</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>RBL</t>
         </is>
       </c>
-      <c r="G17" t="n">
+      <c r="G29" t="n">
         <v>98</v>
       </c>
-      <c r="H17" t="n">
+      <c r="H29" t="n">
         <v>23</v>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>HL60121 SET</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>BR</t>
         </is>
       </c>
-      <c r="P17" t="n">
+      <c r="P29" t="n">
         <v>74</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="Q29" t="n">
         <v>23.5</v>
       </c>
     </row>
-    <row r="18">
-      <c r="E18" t="inlineStr">
+    <row r="30">
+      <c r="E30" t="inlineStr">
         <is>
           <t>CR20202</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>RUST</t>
         </is>
       </c>
-      <c r="G18" t="n">
+      <c r="G30" t="n">
         <v>62</v>
       </c>
-      <c r="H18" t="n">
+      <c r="H30" t="n">
         <v>23</v>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>HL60121 SET</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>CF</t>
         </is>
       </c>
-      <c r="P18" t="n">
+      <c r="P30" t="n">
         <v>105</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="Q30" t="n">
         <v>23.5</v>
       </c>
     </row>
-    <row r="19">
-      <c r="E19" t="inlineStr">
+    <row r="31">
+      <c r="E31" t="inlineStr">
         <is>
           <t>CR20202</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>TP</t>
         </is>
       </c>
-      <c r="G19" t="n">
+      <c r="G31" t="n">
         <v>12</v>
       </c>
-      <c r="H19" t="n">
+      <c r="H31" t="n">
         <v>23</v>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>HL60121 SET</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>KHA</t>
         </is>
       </c>
-      <c r="P19" t="n">
+      <c r="P31" t="n">
         <v>42</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="Q31" t="n">
         <v>23.5</v>
       </c>
     </row>
-    <row r="20">
-      <c r="N20" t="inlineStr">
+    <row r="32">
+      <c r="N32" t="inlineStr">
         <is>
           <t>HL60121 SET</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>ST</t>
         </is>
       </c>
-      <c r="P20" t="n">
+      <c r="P32" t="n">
         <v>1</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="Q32" t="n">
         <v>23.5</v>
       </c>
     </row>
-    <row r="41">
-      <c r="E41" t="inlineStr">
+    <row r="77">
+      <c r="E77" t="inlineStr">
         <is>
           <t>HL60143 SET</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="F77" t="inlineStr">
         <is>
           <t>BG</t>
         </is>
       </c>
-      <c r="G41" t="n">
+      <c r="G77" t="n">
         <v>123</v>
       </c>
-      <c r="H41" t="n">
+      <c r="H77" t="n">
         <v>23.25</v>
       </c>
     </row>
-    <row r="42">
-      <c r="E42" t="inlineStr">
+    <row r="78">
+      <c r="E78" t="inlineStr">
         <is>
           <t>HL60143 SET</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="F78" t="inlineStr">
         <is>
           <t>BK</t>
         </is>
       </c>
-      <c r="G42" t="n">
+      <c r="G78" t="n">
         <v>434</v>
       </c>
-      <c r="H42" t="n">
+      <c r="H78" t="n">
         <v>23.25</v>
       </c>
     </row>
-    <row r="43">
-      <c r="E43" t="inlineStr">
+    <row r="79">
+      <c r="E79" t="inlineStr">
         <is>
           <t>HL60143 SET</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F79" t="inlineStr">
         <is>
           <t>BL</t>
         </is>
       </c>
-      <c r="G43" t="n">
+      <c r="G79" t="n">
         <v>19</v>
       </c>
-      <c r="H43" t="n">
+      <c r="H79" t="n">
         <v>23.25</v>
       </c>
     </row>
-    <row r="44">
-      <c r="E44" t="inlineStr">
+    <row r="80">
+      <c r="E80" t="inlineStr">
         <is>
           <t>HL60143 SET</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="F80" t="inlineStr">
         <is>
           <t>BR</t>
         </is>
       </c>
-      <c r="G44" t="n">
+      <c r="G80" t="n">
         <v>202</v>
       </c>
-      <c r="H44" t="n">
+      <c r="H80" t="n">
         <v>23.25</v>
       </c>
     </row>
-    <row r="45">
-      <c r="E45" t="inlineStr">
+    <row r="81">
+      <c r="E81" t="inlineStr">
         <is>
           <t>HL60143 SET</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F81" t="inlineStr">
         <is>
           <t>KHA</t>
         </is>
       </c>
-      <c r="G45" t="n">
+      <c r="G81" t="n">
         <v>101</v>
       </c>
-      <c r="H45" t="n">
+      <c r="H81" t="n">
         <v>23.25</v>
       </c>
     </row>
-    <row r="46">
-      <c r="E46" t="inlineStr">
+    <row r="82">
+      <c r="E82" t="inlineStr">
         <is>
           <t>HL60143 SET</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F82" t="inlineStr">
         <is>
           <t>TP</t>
         </is>
       </c>
-      <c r="G46" t="n">
+      <c r="G82" t="n">
         <v>91</v>
       </c>
-      <c r="H46" t="n">
+      <c r="H82" t="n">
         <v>23.25</v>
       </c>
     </row>

--- a/inStockInventory_20260915.xlsx
+++ b/inStockInventory_20260915.xlsx
@@ -180,7 +180,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>26</row>
+      <row>24</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2743200" cy="3876675"/>
@@ -205,7 +205,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>26</row>
+      <row>24</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2743200" cy="3876675"/>
@@ -230,7 +230,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>76</row>
+      <row>47</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2743200" cy="3867150"/>
@@ -543,7 +543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q82"/>
+  <dimension ref="A1:Q53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -752,6 +752,74 @@
         <v>23.5</v>
       </c>
     </row>
+    <row r="25">
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>CR20202</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>BK</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>163</v>
+      </c>
+      <c r="H25" t="n">
+        <v>23</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>HL60121 SET</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>BGY</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>CR20202</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>GY</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>89</v>
+      </c>
+      <c r="H26" t="n">
+        <v>23</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>HL60121 SET</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>BK</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>250</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>23.5</v>
+      </c>
+    </row>
     <row r="27">
       <c r="E27" t="inlineStr">
         <is>
@@ -760,11 +828,11 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>BK</t>
+          <t>RBL</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>163</v>
+        <v>98</v>
       </c>
       <c r="H27" t="n">
         <v>23</v>
@@ -776,11 +844,11 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>BGY</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>7</v>
+        <v>74</v>
       </c>
       <c r="Q27" t="n">
         <v>23.5</v>
@@ -794,11 +862,11 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>GY</t>
+          <t>RUST</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>89</v>
+        <v>62</v>
       </c>
       <c r="H28" t="n">
         <v>23</v>
@@ -810,11 +878,11 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>BK</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="P28" t="n">
-        <v>250</v>
+        <v>105</v>
       </c>
       <c r="Q28" t="n">
         <v>23.5</v>
@@ -828,11 +896,11 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>RBL</t>
+          <t>TP</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>98</v>
+        <v>12</v>
       </c>
       <c r="H29" t="n">
         <v>23</v>
@@ -844,33 +912,17 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="Q29" t="n">
         <v>23.5</v>
       </c>
     </row>
     <row r="30">
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>CR20202</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>RUST</t>
-        </is>
-      </c>
-      <c r="G30" t="n">
-        <v>62</v>
-      </c>
-      <c r="H30" t="n">
-        <v>23</v>
-      </c>
       <c r="N30" t="inlineStr">
         <is>
           <t>HL60121 SET</t>
@@ -878,173 +930,121 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>ST</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>105</v>
+        <v>1</v>
       </c>
       <c r="Q30" t="n">
         <v>23.5</v>
       </c>
     </row>
-    <row r="31">
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>CR20202</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
+    <row r="48">
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>HL60143 SET</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>BG</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>123</v>
+      </c>
+      <c r="H48" t="n">
+        <v>23.25</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>HL60143 SET</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>BK</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>434</v>
+      </c>
+      <c r="H49" t="n">
+        <v>23.25</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>HL60143 SET</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>BL</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>19</v>
+      </c>
+      <c r="H50" t="n">
+        <v>23.25</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>HL60143 SET</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>202</v>
+      </c>
+      <c r="H51" t="n">
+        <v>23.25</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>HL60143 SET</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>KHA</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>101</v>
+      </c>
+      <c r="H52" t="n">
+        <v>23.25</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>HL60143 SET</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
         <is>
           <t>TP</t>
         </is>
       </c>
-      <c r="G31" t="n">
-        <v>12</v>
-      </c>
-      <c r="H31" t="n">
-        <v>23</v>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>HL60121 SET</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>KHA</t>
-        </is>
-      </c>
-      <c r="P31" t="n">
-        <v>42</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>23.5</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>HL60121 SET</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>ST</t>
-        </is>
-      </c>
-      <c r="P32" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>23.5</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>HL60143 SET</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>BG</t>
-        </is>
-      </c>
-      <c r="G77" t="n">
-        <v>123</v>
-      </c>
-      <c r="H77" t="n">
-        <v>23.25</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>HL60143 SET</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>BK</t>
-        </is>
-      </c>
-      <c r="G78" t="n">
-        <v>434</v>
-      </c>
-      <c r="H78" t="n">
-        <v>23.25</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>HL60143 SET</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>BL</t>
-        </is>
-      </c>
-      <c r="G79" t="n">
-        <v>19</v>
-      </c>
-      <c r="H79" t="n">
-        <v>23.25</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>HL60143 SET</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>BR</t>
-        </is>
-      </c>
-      <c r="G80" t="n">
-        <v>202</v>
-      </c>
-      <c r="H80" t="n">
-        <v>23.25</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>HL60143 SET</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>KHA</t>
-        </is>
-      </c>
-      <c r="G81" t="n">
-        <v>101</v>
-      </c>
-      <c r="H81" t="n">
-        <v>23.25</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>HL60143 SET</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>TP</t>
-        </is>
-      </c>
-      <c r="G82" t="n">
+      <c r="G53" t="n">
         <v>91</v>
       </c>
-      <c r="H82" t="n">
+      <c r="H53" t="n">
         <v>23.25</v>
       </c>
     </row>

--- a/inStockInventory_20260915.xlsx
+++ b/inStockInventory_20260915.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="inStockInventory" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
